--- a/data/trans_orig/P36B08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B08-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2007</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25278</t>
+          <t>25050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>51462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82994</t>
+          <t>83496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>44478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76422</t>
+          <t>73515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103651</t>
+          <t>102767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147904</t>
+          <t>145401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>257408</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>319082</t>
+          <t>316104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>263727</t>
+          <t>263069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>322164</t>
+          <t>321699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>540111</t>
+          <t>537014</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>621851</t>
+          <t>623593</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367116</t>
+          <t>367854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>429362</t>
+          <t>428501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>545640</t>
+          <t>549712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>618341</t>
+          <t>618571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>934043</t>
+          <t>933105</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1023007</t>
+          <t>1025516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>237438</t>
+          <t>238340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>292360</t>
+          <t>293992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340462</t>
+          <t>340793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>409160</t>
+          <t>404065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>595610</t>
+          <t>594123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>684095</t>
+          <t>676490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40537</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68314</t>
+          <t>67561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41607</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66240</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99550</t>
+          <t>101888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115843</t>
+          <t>116024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160789</t>
+          <t>163188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59764</t>
+          <t>58715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92454</t>
+          <t>92497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181825</t>
+          <t>184358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240044</t>
+          <t>242250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>423958</t>
+          <t>422701</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>497108</t>
+          <t>496515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347487</t>
+          <t>344069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>413618</t>
+          <t>410141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>788270</t>
+          <t>790685</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>889908</t>
+          <t>891702</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>715790</t>
+          <t>712156</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>795724</t>
+          <t>794850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>647842</t>
+          <t>651209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>729657</t>
+          <t>729227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1388461</t>
+          <t>1388944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1501649</t>
+          <t>1503590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256249</t>
+          <t>256871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321378</t>
+          <t>322294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381101</t>
+          <t>383223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>452093</t>
+          <t>450929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657551</t>
+          <t>651091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754214</t>
+          <t>750102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36928</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29760</t>
+          <t>29064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55699</t>
+          <t>54250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133932</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177055</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99959</t>
+          <t>99976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137862</t>
+          <t>136472</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>244589</t>
+          <t>245868</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>308796</t>
+          <t>302373</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>208678</t>
+          <t>208419</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>255664</t>
+          <t>256218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>164803</t>
+          <t>167824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>206899</t>
+          <t>208090</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>384479</t>
+          <t>388201</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>451616</t>
+          <t>454574</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113887</t>
+          <t>113241</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155255</t>
+          <t>152925</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131995</t>
+          <t>130965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173343</t>
+          <t>172587</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>255765</t>
+          <t>253313</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>317650</t>
+          <t>310785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57868</t>
+          <t>56905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90777</t>
+          <t>90075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56088</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95422</t>
+          <t>96065</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137291</t>
+          <t>137659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>200833</t>
+          <t>199044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258007</t>
+          <t>258577</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123193</t>
+          <t>124038</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170664</t>
+          <t>170982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>340179</t>
+          <t>336777</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413692</t>
+          <t>417686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>854576</t>
+          <t>851550</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>955996</t>
+          <t>958089</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>744815</t>
+          <t>743328</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>839467</t>
+          <t>840486</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1622406</t>
+          <t>1621570</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1762318</t>
+          <t>1767594</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1330178</t>
+          <t>1328608</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1440369</t>
+          <t>1449638</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1408094</t>
+          <t>1401220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1521099</t>
+          <t>1518811</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2769166</t>
+          <t>2757092</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2922925</t>
+          <t>2917282</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>639768</t>
+          <t>635779</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>736864</t>
+          <t>729273</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>889243</t>
+          <t>890788</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>996320</t>
+          <t>995068</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1552715</t>
+          <t>1552484</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1698620</t>
+          <t>1696921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2012</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29812</t>
+          <t>29534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49831</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28710</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>53409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33614</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68551</t>
+          <t>68579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103832</t>
+          <t>105523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179216</t>
+          <t>176470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>229797</t>
+          <t>230186</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171316</t>
+          <t>172351</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223679</t>
+          <t>221935</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>363106</t>
+          <t>362941</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>436467</t>
+          <t>437175</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>263436</t>
+          <t>265857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>322703</t>
+          <t>323719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>384323</t>
+          <t>384896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>451871</t>
+          <t>451954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>663763</t>
+          <t>667176</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>757497</t>
+          <t>757114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384865</t>
+          <t>384411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445430</t>
+          <t>449918</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>626141</t>
+          <t>625565</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>700428</t>
+          <t>700760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1023967</t>
+          <t>1029763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1122758</t>
+          <t>1127083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>23243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46872</t>
+          <t>45994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37629</t>
+          <t>37134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65498</t>
+          <t>65328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79979</t>
+          <t>80221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117894</t>
+          <t>119547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70123</t>
+          <t>70107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128069</t>
+          <t>129233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178614</t>
+          <t>177257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431986</t>
+          <t>432121</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>509607</t>
+          <t>511051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>294236</t>
+          <t>294143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>361621</t>
+          <t>361176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>749795</t>
+          <t>743216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>847232</t>
+          <t>850168</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>689263</t>
+          <t>685417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>778207</t>
+          <t>775834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>581278</t>
+          <t>578667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>663038</t>
+          <t>660588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1296330</t>
+          <t>1293582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1412800</t>
+          <t>1409284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590845</t>
+          <t>586699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>674709</t>
+          <t>672232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>690837</t>
+          <t>689031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>776534</t>
+          <t>774660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1304532</t>
+          <t>1304124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1424652</t>
+          <t>1419312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,77 +5070,77 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2079</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>6129</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>12400</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2079</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7240</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>6129</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2116</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>12410</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>11778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84245</t>
+          <t>86012</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>122063</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47127</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76946</t>
+          <t>78559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>138429</t>
+          <t>140204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>189595</t>
+          <t>190145</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157528</t>
+          <t>157866</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>201832</t>
+          <t>201102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123104</t>
+          <t>123753</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165512</t>
+          <t>164500</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>295097</t>
+          <t>290851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>353016</t>
+          <t>352322</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160509</t>
+          <t>161053</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205991</t>
+          <t>206724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219790</t>
+          <t>222107</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267301</t>
+          <t>266281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395456</t>
+          <t>395480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>459691</t>
+          <t>458246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40606</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71462</t>
+          <t>72379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>25819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49710</t>
+          <t>50623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74892</t>
+          <t>73167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114381</t>
+          <t>112924</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126830</t>
+          <t>126730</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175911</t>
+          <t>174997</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83879</t>
+          <t>84360</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126623</t>
+          <t>126464</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>221366</t>
+          <t>221437</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>285256</t>
+          <t>284482</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>726505</t>
+          <t>727020</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>828329</t>
+          <t>827814</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>542165</t>
+          <t>539099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>633064</t>
+          <t>630426</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1300303</t>
+          <t>1293235</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1436523</t>
+          <t>1434258</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1148206</t>
+          <t>1142498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1257192</t>
+          <t>1261523</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1127451</t>
+          <t>1126313</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1244490</t>
+          <t>1237351</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2303502</t>
+          <t>2302041</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2468609</t>
+          <t>2465518</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1171249</t>
+          <t>1169908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1285834</t>
+          <t>1286748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1577008</t>
+          <t>1576231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1698782</t>
+          <t>1694646</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2780522</t>
+          <t>2783405</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2959783</t>
+          <t>2945326</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2016</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31389</t>
+          <t>31348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35697</t>
+          <t>35263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34940</t>
+          <t>35303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>34402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63442</t>
+          <t>61187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123150</t>
+          <t>123449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164250</t>
+          <t>166168</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148819</t>
+          <t>145228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>198722</t>
+          <t>197748</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>282342</t>
+          <t>282034</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>346119</t>
+          <t>344788</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>328838</t>
+          <t>333513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>386720</t>
+          <t>387279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>376493</t>
+          <t>379308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>443917</t>
+          <t>444908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>723104</t>
+          <t>729939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>808299</t>
+          <t>810793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191888</t>
+          <t>194005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242255</t>
+          <t>242713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341774</t>
+          <t>343279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>406361</t>
+          <t>407084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>551028</t>
+          <t>554124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>633435</t>
+          <t>634279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>19426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>39680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37980</t>
+          <t>37691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41531</t>
+          <t>41829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71562</t>
+          <t>72639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79066</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118057</t>
+          <t>117281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43560</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73575</t>
+          <t>74199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131406</t>
+          <t>128376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180333</t>
+          <t>178634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>468855</t>
+          <t>467370</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>550040</t>
+          <t>549628</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>374535</t>
+          <t>376325</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>447971</t>
+          <t>446906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>862906</t>
+          <t>872262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>975141</t>
+          <t>982716</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>869666</t>
+          <t>873519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>962811</t>
+          <t>962397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>803017</t>
+          <t>800633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>890068</t>
+          <t>889986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1704574</t>
+          <t>1701745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1828890</t>
+          <t>1827046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>471614</t>
+          <t>472676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>548483</t>
+          <t>549516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>596947</t>
+          <t>593533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>677007</t>
+          <t>678681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1091649</t>
+          <t>1087212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1212118</t>
+          <t>1203845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>30363</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43780</t>
+          <t>41862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82064</t>
+          <t>81421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120241</t>
+          <t>119498</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68431</t>
+          <t>66405</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99327</t>
+          <t>98858</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>154384</t>
+          <t>157437</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206092</t>
+          <t>205189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>200168</t>
+          <t>200449</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>249756</t>
+          <t>247902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196469</t>
+          <t>196980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243719</t>
+          <t>246928</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>410515</t>
+          <t>407760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>477570</t>
+          <t>472694</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180835</t>
+          <t>179457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228355</t>
+          <t>227591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201747</t>
+          <t>205409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251026</t>
+          <t>252771</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>402254</t>
+          <t>400135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466901</t>
+          <t>465563</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27658</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50418</t>
+          <t>51506</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>31407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58019</t>
+          <t>58536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65360</t>
+          <t>63858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102749</t>
+          <t>101155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119624</t>
+          <t>116800</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167051</t>
+          <t>165182</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74097</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111098</t>
+          <t>111851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>200063</t>
+          <t>197936</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261509</t>
+          <t>260922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>705621</t>
+          <t>706525</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>802834</t>
+          <t>798768</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>615803</t>
+          <t>616651</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>709054</t>
+          <t>710570</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1345041</t>
+          <t>1347089</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1480699</t>
+          <t>1486207</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1442995</t>
+          <t>1439814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1557956</t>
+          <t>1557477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1417422</t>
+          <t>1417957</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1534784</t>
+          <t>1531639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2891947</t>
+          <t>2893707</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3064447</t>
+          <t>3063849</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>874375</t>
+          <t>878845</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>983453</t>
+          <t>989711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1183047</t>
+          <t>1186803</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1296759</t>
+          <t>1300261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2093081</t>
+          <t>2097721</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2257943</t>
+          <t>2254929</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B08-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25050</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51462</t>
+          <t>51482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83496</t>
+          <t>81856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>43828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73515</t>
+          <t>72811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102767</t>
+          <t>103926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145401</t>
+          <t>145484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>258784</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>316104</t>
+          <t>316811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>260981</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>321699</t>
+          <t>320827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>537014</t>
+          <t>542601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>623593</t>
+          <t>617805</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367854</t>
+          <t>365488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>428501</t>
+          <t>425724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>549712</t>
+          <t>551019</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>618571</t>
+          <t>622836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,47 +1121,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>47,36%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>980589</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>932030</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>1028759</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>41,8%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>47,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>980589</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>933105</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1025516</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>41,8%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238340</t>
+          <t>239019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>293992</t>
+          <t>293927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340793</t>
+          <t>343042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>404065</t>
+          <t>409954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>594123</t>
+          <t>598027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>676490</t>
+          <t>684198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>40469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67561</t>
+          <t>67880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>41175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>66123</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101888</t>
+          <t>103345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116024</t>
+          <t>115576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163188</t>
+          <t>160985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58715</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92497</t>
+          <t>93614</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>184358</t>
+          <t>184775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242250</t>
+          <t>242541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>422701</t>
+          <t>424380</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>496515</t>
+          <t>496139</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>344069</t>
+          <t>345416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>410141</t>
+          <t>412730</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>790685</t>
+          <t>786860</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>891702</t>
+          <t>887112</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>712156</t>
+          <t>714056</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>794850</t>
+          <t>799958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>651209</t>
+          <t>647845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>729227</t>
+          <t>731719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1388944</t>
+          <t>1384600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1503590</t>
+          <t>1504774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256871</t>
+          <t>258431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322294</t>
+          <t>322581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>383223</t>
+          <t>379665</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>450929</t>
+          <t>449038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651091</t>
+          <t>651877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750102</t>
+          <t>752195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>37264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23430</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29064</t>
+          <t>29008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>53657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>133853</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>179754</t>
+          <t>179097</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99976</t>
+          <t>103032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>136472</t>
+          <t>140121</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>245868</t>
+          <t>244809</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>302373</t>
+          <t>303436</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>208419</t>
+          <t>206937</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>256218</t>
+          <t>254791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>167824</t>
+          <t>164035</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>208090</t>
+          <t>206873</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>388201</t>
+          <t>385085</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>454574</t>
+          <t>447731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113241</t>
+          <t>112006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152925</t>
+          <t>154543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130965</t>
+          <t>130818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172587</t>
+          <t>171924</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253313</t>
+          <t>259514</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310785</t>
+          <t>319773</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>58615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>93187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31621</t>
+          <t>30571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>54747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,47 +2828,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>114452</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>93390</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>136831</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>114452</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>96065</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>137659</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199044</t>
+          <t>198201</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258577</t>
+          <t>259674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124038</t>
+          <t>124714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170982</t>
+          <t>172489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>336777</t>
+          <t>334398</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>417686</t>
+          <t>412505</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>851550</t>
+          <t>849640</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>958089</t>
+          <t>952507</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>743328</t>
+          <t>739890</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>840486</t>
+          <t>836129</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1621570</t>
+          <t>1625428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1767594</t>
+          <t>1768899</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1328608</t>
+          <t>1330399</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1449638</t>
+          <t>1440650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1401220</t>
+          <t>1405585</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1518811</t>
+          <t>1515839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2757092</t>
+          <t>2770306</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2917282</t>
+          <t>2927119</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>635779</t>
+          <t>640610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>729273</t>
+          <t>731622</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>890788</t>
+          <t>887831</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>995068</t>
+          <t>990314</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1552484</t>
+          <t>1562661</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1696921</t>
+          <t>1698029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29534</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>24624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51484</t>
+          <t>48883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27919</t>
+          <t>28340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>53148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32305</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60190</t>
+          <t>61712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68579</t>
+          <t>68397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105523</t>
+          <t>106503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176470</t>
+          <t>178250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230186</t>
+          <t>233540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>172351</t>
+          <t>169147</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>221935</t>
+          <t>223298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>362941</t>
+          <t>363621</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>437175</t>
+          <t>439170</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>265857</t>
+          <t>264925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>323719</t>
+          <t>322865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>384896</t>
+          <t>382514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>451954</t>
+          <t>454446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>667176</t>
+          <t>662949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>757114</t>
+          <t>755685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384411</t>
+          <t>382498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449918</t>
+          <t>447445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>625565</t>
+          <t>624256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>700760</t>
+          <t>702214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1029763</t>
+          <t>1024138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1127083</t>
+          <t>1125744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45994</t>
+          <t>45005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26778</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37134</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65328</t>
+          <t>66831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80221</t>
+          <t>77909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119547</t>
+          <t>117898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39894</t>
+          <t>40395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70107</t>
+          <t>69479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129233</t>
+          <t>128712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177257</t>
+          <t>178477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>432121</t>
+          <t>437340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>511051</t>
+          <t>513005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>294143</t>
+          <t>292851</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>361176</t>
+          <t>358256</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>743216</t>
+          <t>749279</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>850168</t>
+          <t>852501</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>685417</t>
+          <t>683823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>775834</t>
+          <t>773528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>578667</t>
+          <t>580368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>660588</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1293582</t>
+          <t>1292381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1409284</t>
+          <t>1413240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>586699</t>
+          <t>586813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>672232</t>
+          <t>670524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689031</t>
+          <t>689958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>774660</t>
+          <t>773514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1304124</t>
+          <t>1293069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1419312</t>
+          <t>1419499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>26648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86012</t>
+          <t>83215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>122063</t>
+          <t>121727</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47876</t>
+          <t>46776</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78559</t>
+          <t>77440</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>140204</t>
+          <t>140624</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>190145</t>
+          <t>190469</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157866</t>
+          <t>159588</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>201102</t>
+          <t>203101</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123753</t>
+          <t>124722</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>164500</t>
+          <t>165270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290851</t>
+          <t>292959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>352322</t>
+          <t>352890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161053</t>
+          <t>160499</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206724</t>
+          <t>203683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222107</t>
+          <t>222152</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266281</t>
+          <t>265080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395480</t>
+          <t>397229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>458246</t>
+          <t>461854</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>71848</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>26177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50623</t>
+          <t>51645</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73167</t>
+          <t>75166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112924</t>
+          <t>113809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126730</t>
+          <t>126083</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174997</t>
+          <t>173729</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>84360</t>
+          <t>86194</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126464</t>
+          <t>125564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>221437</t>
+          <t>222277</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>284482</t>
+          <t>287651</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>727020</t>
+          <t>732488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>827814</t>
+          <t>830310</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>539099</t>
+          <t>540824</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>630426</t>
+          <t>630339</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1293235</t>
+          <t>1295166</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1434258</t>
+          <t>1433395</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1142498</t>
+          <t>1144305</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1261523</t>
+          <t>1260012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1126313</t>
+          <t>1126692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1237351</t>
+          <t>1239826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2302041</t>
+          <t>2312145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2465518</t>
+          <t>2470379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1169908</t>
+          <t>1168609</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1286748</t>
+          <t>1289715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1576231</t>
+          <t>1575076</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1694646</t>
+          <t>1698792</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2783405</t>
+          <t>2775146</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2945326</t>
+          <t>2945849</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19719</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31348</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35263</t>
+          <t>34836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35303</t>
+          <t>34932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61187</t>
+          <t>61563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123449</t>
+          <t>124283</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>166168</t>
+          <t>164929</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145228</t>
+          <t>147034</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>197748</t>
+          <t>196264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>282034</t>
+          <t>283321</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344788</t>
+          <t>345556</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>333513</t>
+          <t>330120</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>387279</t>
+          <t>383975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>379308</t>
+          <t>380373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444908</t>
+          <t>446134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>729939</t>
+          <t>726387</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>810793</t>
+          <t>811912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194005</t>
+          <t>194965</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242713</t>
+          <t>239365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343279</t>
+          <t>343748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>407084</t>
+          <t>408000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>554124</t>
+          <t>547984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>634279</t>
+          <t>628496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19426</t>
+          <t>19437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>39825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37691</t>
+          <t>37565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41829</t>
+          <t>40146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72639</t>
+          <t>69766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77450</t>
+          <t>78952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117281</t>
+          <t>119531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43490</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>73137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128376</t>
+          <t>131205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178634</t>
+          <t>180367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>467370</t>
+          <t>471593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>549628</t>
+          <t>552809</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>376325</t>
+          <t>375453</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>446906</t>
+          <t>444451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>872262</t>
+          <t>865470</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>982716</t>
+          <t>978684</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>873519</t>
+          <t>871379</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>962397</t>
+          <t>964287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>800633</t>
+          <t>804735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>889986</t>
+          <t>891262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1701745</t>
+          <t>1697059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1827046</t>
+          <t>1822495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>472676</t>
+          <t>472618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>549516</t>
+          <t>550519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593533</t>
+          <t>596048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>678681</t>
+          <t>681877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1087212</t>
+          <t>1094840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1203845</t>
+          <t>1213816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30363</t>
+          <t>32240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41862</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81421</t>
+          <t>83315</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119498</t>
+          <t>120059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66405</t>
+          <t>66438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98858</t>
+          <t>100499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157437</t>
+          <t>156742</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>205189</t>
+          <t>206069</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>200449</t>
+          <t>201302</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>247902</t>
+          <t>246283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196980</t>
+          <t>196135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246928</t>
+          <t>242947</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>407760</t>
+          <t>412038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>472694</t>
+          <t>476463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179457</t>
+          <t>179078</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227591</t>
+          <t>225451</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,47 +8481,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>41,38%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>228574</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>205279</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>252209</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>41,77%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>228574</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>205409</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>252771</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400135</t>
+          <t>395193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>465563</t>
+          <t>462301</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>27826</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31407</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58536</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63858</t>
+          <t>65638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101155</t>
+          <t>100985</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116800</t>
+          <t>118994</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165182</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72187</t>
+          <t>74277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111851</t>
+          <t>114471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197936</t>
+          <t>203344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>260922</t>
+          <t>265240</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>706525</t>
+          <t>702862</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>798768</t>
+          <t>801714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>616651</t>
+          <t>616955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>710570</t>
+          <t>704282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1347089</t>
+          <t>1341948</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1486207</t>
+          <t>1486585</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1439814</t>
+          <t>1439217</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1557477</t>
+          <t>1556372</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1417957</t>
+          <t>1416312</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1531639</t>
+          <t>1536541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2893707</t>
+          <t>2886165</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3063849</t>
+          <t>3054975</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>878845</t>
+          <t>878414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>989711</t>
+          <t>979752</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1186803</t>
+          <t>1183348</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1300261</t>
+          <t>1301390</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2097721</t>
+          <t>2094126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2254929</t>
+          <t>2254097</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
